--- a/Tendo_Monitoring_data/20260330_v1pesorate.xlsx
+++ b/Tendo_Monitoring_data/20260330_v1pesorate.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tonikph-my.sharepoint.com/personal/dchakroborti_tonikbank_com/Documents/MyStuff/Data Engineering/Tendo_Model_Monitoring_Dashboards_Requirement/Tendo_Monitoring_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_7E0DE31C64119237C709D420C472E178255D5F02" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4C4D257-C058-40AD-859B-2F395878F89F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="v1pesorate" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -77,11 +58,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,13 +69,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -137,38 +108,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -206,7 +166,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -240,7 +200,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -275,10 +234,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -451,19 +409,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,7 +433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -491,23 +441,22 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>18099479.5</v>
+        <v>18682278.5</v>
       </c>
       <c r="D2">
-        <v>6474457.9740000023</v>
+        <v>6697841.273000002</v>
       </c>
       <c r="E2">
-        <v>5921354.8780000024</v>
+        <v>6183184.945000001</v>
       </c>
       <c r="F2">
-        <v>4070457.023</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.62869463966652639</v>
-      </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4321989.908</v>
+      </c>
+      <c r="G2">
+        <v>64.5281028892486</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -515,23 +464,22 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>15548592</v>
+        <v>16277842</v>
       </c>
       <c r="D3">
-        <v>4972060.6770000011</v>
+        <v>5261633.010999997</v>
       </c>
       <c r="E3">
-        <v>5054510.8049999997</v>
+        <v>5348508.382999998</v>
       </c>
       <c r="F3">
-        <v>3199942.62</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.64358478865763824</v>
-      </c>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3452267.106999999</v>
+      </c>
+      <c r="G3">
+        <v>65.61208468516661</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -539,23 +487,22 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>11426397</v>
+        <v>11917418</v>
       </c>
       <c r="D4">
-        <v>3531153.4410000001</v>
+        <v>3755108.951000001</v>
       </c>
       <c r="E4">
-        <v>3552276.5439999988</v>
+        <v>3716463.007999999</v>
       </c>
       <c r="F4">
-        <v>2572754.1469999989</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.72858746865200275</v>
-      </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>2736940.610999999</v>
+      </c>
+      <c r="G4">
+        <v>72.88578431981688</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -563,23 +510,22 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>17698526</v>
+        <v>18332580.5</v>
       </c>
       <c r="D5">
-        <v>8486248.5649999976</v>
+        <v>8723711.625999995</v>
       </c>
       <c r="E5">
-        <v>8936645.2860000022</v>
+        <v>9245608.763</v>
       </c>
       <c r="F5">
-        <v>6730109.5399999972</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.79306061900627323</v>
-      </c>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7025055.776</v>
+      </c>
+      <c r="G5">
+        <v>80.52828975986148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -587,23 +533,22 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>24908159.5</v>
+        <v>25594467.5</v>
       </c>
       <c r="D6">
-        <v>13862360.494000001</v>
+        <v>14187557.10999999</v>
       </c>
       <c r="E6">
-        <v>15152954.71900001</v>
+        <v>15532475.05</v>
       </c>
       <c r="F6">
-        <v>11796839.098999999</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.85099785884994039</v>
-      </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12161044.26999999</v>
+      </c>
+      <c r="G6">
+        <v>85.71626655464438</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -611,23 +556,22 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>13363094.5</v>
+        <v>13726164</v>
       </c>
       <c r="D7">
-        <v>7588288.7200000044</v>
+        <v>7727307.009000003</v>
       </c>
       <c r="E7">
-        <v>8508873.4800000023</v>
+        <v>8704355.414999999</v>
       </c>
       <c r="F7">
-        <v>6555535.5470000003</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.86390170285982426</v>
-      </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>6714499.653999998</v>
+      </c>
+      <c r="G7">
+        <v>86.89313943628242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -635,21 +579,20 @@
         <v>12</v>
       </c>
       <c r="C8">
-        <v>5370659.5</v>
+        <v>5592677.5</v>
       </c>
       <c r="D8">
-        <v>1739411.404000001</v>
+        <v>1801086.842</v>
       </c>
       <c r="E8">
-        <v>3017319.128</v>
+        <v>3144301.594999999</v>
       </c>
       <c r="F8">
-        <v>1739411.404000001</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2"/>
+        <v>1847733.695000001</v>
+      </c>
+      <c r="G8">
+        <v>102.58992803191</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
